--- a/templates/excel-templates/experimentSamples.Genotyping_Array.xlsx
+++ b/templates/excel-templates/experimentSamples.Genotyping_Array.xlsx
@@ -161,7 +161,7 @@
     <t>genotyping_array</t>
   </si>
   <si>
-    <t>Schema Version 3.34</t>
+    <t>Schema Version 3.35</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>

--- a/templates/excel-templates/experimentSamples.Genotyping_Array.xlsx
+++ b/templates/excel-templates/experimentSamples.Genotyping_Array.xlsx
@@ -161,7 +161,7 @@
     <t>genotyping_array</t>
   </si>
   <si>
-    <t>Schema Version 3.35</t>
+    <t>Schema Version 3.36</t>
   </si>
   <si>
     <t>Please do not delete or edit this column</t>
